--- a/datasets/day1_excel_foundations/01_interface_and_workbook_basics/practice_start.xlsx
+++ b/datasets/day1_excel_foundations/01_interface_and_workbook_basics/practice_start.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -557,7 +557,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Chen Li</t>
+          <t>Amara Otieno</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Emily Brown</t>
+          <t>Chanda Phiri</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aarav Kumar</t>
+          <t>Chipo Marufu</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Michael Miller</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Li Zhang</t>
+          <t>Kudzai Sibanda</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Alex Johnson</t>
+          <t>Tendai Moyo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -982,7 +982,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>O0008  |  29/08/2024  |  Emily Brown  |  MacBook Air M4  |  Laptop  |  1  |  779.2</t>
+          <t>O0008  |  29/08/2024  |  Chanda Phiri  |  MacBook Air M4  |  Laptop  |  1  |  779.2</t>
         </is>
       </c>
     </row>
